--- a/artfynd/A 14438-2025 artfynd.xlsx
+++ b/artfynd/A 14438-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125564426</v>
+        <v>125561750</v>
       </c>
       <c r="B2" t="n">
-        <v>58167</v>
+        <v>57793</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,48 +687,52 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102990</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Orretorp, Orrtorpet, Vg</t>
+          <t>Orretorp, Orretorp, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476881</v>
+        <v>476930</v>
       </c>
       <c r="R2" t="n">
-        <v>6503950</v>
+        <v>6503685</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -760,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -770,7 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Mycket lämplig miljö. Bohål i björkstubbe.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125562606</v>
+        <v>125564426</v>
       </c>
       <c r="B3" t="n">
-        <v>58001</v>
+        <v>58167</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,16 +822,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,11 +839,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>adult</t>
@@ -842,24 +847,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Orretorp, Orretorp, Vg</t>
+          <t>Orretorp, Orrtorpet, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476930</v>
+        <v>476881</v>
       </c>
       <c r="R3" t="n">
-        <v>6503685</v>
+        <v>6503950</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1059,10 +1059,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125561750</v>
+        <v>125562606</v>
       </c>
       <c r="B5" t="n">
-        <v>57793</v>
+        <v>58001</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1071,25 +1071,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1097,9 +1097,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1148,7 +1153,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1158,12 +1163,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Mycket lämplig miljö. Bohål i björkstubbe.</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 14438-2025 artfynd.xlsx
+++ b/artfynd/A 14438-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125561750</v>
+        <v>125562606</v>
       </c>
       <c r="B2" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58019</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,9 +708,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Mycket lämplig miljö. Bohål i björkstubbe.</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,60 +801,59 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125564426</v>
+        <v>125561750</v>
       </c>
       <c r="B3" t="n">
-        <v>58167</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57811</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102990</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Orretorp, Orrtorpet, Vg</t>
+          <t>Orretorp, Orretorp, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476881</v>
+        <v>476930</v>
       </c>
       <c r="R3" t="n">
-        <v>6503950</v>
+        <v>6503685</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -891,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -901,7 +895,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Mycket lämplig miljö. Bohål i björkstubbe.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,15 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125564274</v>
+        <v>125564426</v>
       </c>
       <c r="B4" t="n">
-        <v>58485</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58186</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -944,36 +938,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208250</v>
+        <v>102990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -982,13 +972,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476863</v>
+        <v>476881</v>
       </c>
       <c r="R4" t="n">
-        <v>6503994</v>
+        <v>6503950</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1017,7 +1007,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1027,12 +1017,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Frisk mark i anslutning till sumpdråg. Artbestämning osäker, ev. vanlig groda.</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,15 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125562606</v>
+        <v>125564274</v>
       </c>
       <c r="B5" t="n">
-        <v>58001</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58505</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,21 +1055,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>208250</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1102,11 +1082,6 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1114,17 +1089,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Orretorp, Orretorp, Vg</t>
+          <t>Orretorp, Orrtorpet, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476930</v>
+        <v>476863</v>
       </c>
       <c r="R5" t="n">
-        <v>6503685</v>
+        <v>6503994</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1153,7 +1128,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1163,7 +1138,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Frisk mark i anslutning till sumpdråg. Artbestämning osäker, ev. vanlig groda.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 14438-2025 artfynd.xlsx
+++ b/artfynd/A 14438-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125562606</v>
       </c>
       <c r="B2" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>125564426</v>
       </c>
       <c r="B4" t="n">
-        <v>58186</v>
+        <v>58187</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>125564274</v>
       </c>
       <c r="B5" t="n">
-        <v>58505</v>
+        <v>58506</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 14438-2025 artfynd.xlsx
+++ b/artfynd/A 14438-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125562606</v>
       </c>
       <c r="B2" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>125561750</v>
       </c>
       <c r="B3" t="n">
-        <v>57811</v>
+        <v>57812</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>125564426</v>
       </c>
       <c r="B4" t="n">
-        <v>58187</v>
+        <v>58188</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>125564274</v>
       </c>
       <c r="B5" t="n">
-        <v>58506</v>
+        <v>58507</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 14438-2025 artfynd.xlsx
+++ b/artfynd/A 14438-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125562606</v>
+        <v>125561423</v>
       </c>
       <c r="B2" t="n">
-        <v>58021</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,14 +708,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -725,17 +720,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Orretorp, Orretorp, Vg</t>
+          <t>Björkhaga, Björkhaga, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476930</v>
+        <v>476914</v>
       </c>
       <c r="R2" t="n">
-        <v>6503685</v>
+        <v>6503654</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Bohål i grov asp, fin miljö.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125561750</v>
+        <v>125564426</v>
       </c>
       <c r="B3" t="n">
-        <v>57812</v>
+        <v>58497</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,48 +812,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>102990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Orretorp, Orretorp, Vg</t>
+          <t>Orretorp, Orrtorpet, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476930</v>
+        <v>476881</v>
       </c>
       <c r="R3" t="n">
-        <v>6503685</v>
+        <v>6503950</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -885,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,12 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Mycket lämplig miljö. Bohål i björkstubbe.</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125564426</v>
+        <v>125562606</v>
       </c>
       <c r="B4" t="n">
-        <v>58188</v>
+        <v>58327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,16 +929,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -955,7 +946,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>adult</t>
@@ -963,19 +958,24 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Orretorp, Orrtorpet, Vg</t>
+          <t>Orretorp, Orretorp, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476881</v>
+        <v>476930</v>
       </c>
       <c r="R4" t="n">
-        <v>6503950</v>
+        <v>6503685</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,32 +1044,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125564274</v>
+        <v>125561750</v>
       </c>
       <c r="B5" t="n">
-        <v>58507</v>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208250</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1077,9 +1077,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1089,17 +1089,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Orretorp, Orrtorpet, Vg</t>
+          <t>Orretorp, Orretorp, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476863</v>
+        <v>476930</v>
       </c>
       <c r="R5" t="n">
-        <v>6503994</v>
+        <v>6503685</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1138,12 +1138,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Frisk mark i anslutning till sumpdråg. Artbestämning osäker, ev. vanlig groda.</t>
+          <t>Mycket lämplig miljö. Bohål i björkstubbe.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,6 +1167,132 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125564274</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58815</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Orretorp, Orrtorpet, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>476863</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6503994</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Karlsborg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Undenäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Frisk mark i anslutning till sumpdråg. Artbestämning osäker, ev. vanlig groda.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Boel Nilsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Boel Nilsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14438-2025 artfynd.xlsx
+++ b/artfynd/A 14438-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125561423</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,6 +925,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125564426</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1041,6 +1056,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125562606</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1167,6 +1187,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125561750</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1293,8 +1318,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125564274</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>